--- a/results/onion_s_simulation.xlsx
+++ b/results/onion_s_simulation.xlsx
@@ -7,24 +7,26 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Про звіт" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Калібрація" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Теплова карта J(α,δ)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Деградація" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарії ADMI" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Сценарії DM компоненти" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рівні розподіл" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матриця Маркова С-1" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матриця Маркова С-2" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Матриця Маркова С-3" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Стаціонарні розподіли" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Час досягнення рівня" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Крос-валідація" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Чутливість" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рис. Траєкторії ADMI" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рис. Профілі DM" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рис. Крос-валідація" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Рис. Чутливість" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Calibration" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Heatmap J(α,δ)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Degradation" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios ADMI" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scenarios DM" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Level distribution" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Markov S-1" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Markov S-2" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Markov S-3" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stationary distrib." sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Hitting times" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Multi-horizon" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cross-validation" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig. ADMI trajectories" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig. DM profiles" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig. Multi-horizon" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig. Cross-validation" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fig. Sensitivity" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -209,7 +211,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Рис. Траєкторії ADMI'!B3</f>
+              <f>'Fig. ADMI trajectories'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -227,12 +229,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$A$4:$A$9</f>
+              <f>'Fig. ADMI trajectories'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$B$4:$B$9</f>
+              <f>'Fig. ADMI trajectories'!$B$4:$B$9</f>
             </numRef>
           </val>
         </ser>
@@ -241,7 +243,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Рис. Траєкторії ADMI'!C3</f>
+              <f>'Fig. ADMI trajectories'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -259,12 +261,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$A$4:$A$9</f>
+              <f>'Fig. ADMI trajectories'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$C$4:$C$9</f>
+              <f>'Fig. ADMI trajectories'!$C$4:$C$9</f>
             </numRef>
           </val>
         </ser>
@@ -273,7 +275,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Рис. Траєкторії ADMI'!D3</f>
+              <f>'Fig. ADMI trajectories'!D3</f>
             </strRef>
           </tx>
           <spPr>
@@ -291,12 +293,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$A$4:$A$9</f>
+              <f>'Fig. ADMI trajectories'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$D$4:$D$9</f>
+              <f>'Fig. ADMI trajectories'!$D$4:$D$9</f>
             </numRef>
           </val>
         </ser>
@@ -305,7 +307,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Рис. Траєкторії ADMI'!E3</f>
+              <f>'Fig. ADMI trajectories'!E3</f>
             </strRef>
           </tx>
           <spPr>
@@ -323,12 +325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$A$4:$A$9</f>
+              <f>'Fig. ADMI trajectories'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$E$4:$E$9</f>
+              <f>'Fig. ADMI trajectories'!$E$4:$E$9</f>
             </numRef>
           </val>
         </ser>
@@ -337,7 +339,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Рис. Траєкторії ADMI'!F3</f>
+              <f>'Fig. ADMI trajectories'!F3</f>
             </strRef>
           </tx>
           <spPr>
@@ -355,12 +357,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$A$4:$A$9</f>
+              <f>'Fig. ADMI trajectories'!$A$4:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Траєкторії ADMI'!$F$4:$F$9</f>
+              <f>'Fig. ADMI trajectories'!$F$4:$F$9</f>
             </numRef>
           </val>
         </ser>
@@ -382,7 +384,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Рік</a:t>
+                  <a:t>Year</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -441,7 +443,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Рис. Профілі DM'!B3</f>
+              <f>'Fig. DM profiles'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -459,12 +461,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Профілі DM'!$A$4:$A$10</f>
+              <f>'Fig. DM profiles'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Профілі DM'!$B$4:$B$10</f>
+              <f>'Fig. DM profiles'!$B$4:$B$10</f>
             </numRef>
           </val>
         </ser>
@@ -473,7 +475,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Рис. Профілі DM'!C3</f>
+              <f>'Fig. DM profiles'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -491,12 +493,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Профілі DM'!$A$4:$A$10</f>
+              <f>'Fig. DM profiles'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Профілі DM'!$C$4:$C$10</f>
+              <f>'Fig. DM profiles'!$C$4:$C$10</f>
             </numRef>
           </val>
         </ser>
@@ -505,7 +507,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Рис. Профілі DM'!D3</f>
+              <f>'Fig. DM profiles'!D3</f>
             </strRef>
           </tx>
           <spPr>
@@ -523,12 +525,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Профілі DM'!$A$4:$A$10</f>
+              <f>'Fig. DM profiles'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Профілі DM'!$D$4:$D$10</f>
+              <f>'Fig. DM profiles'!$D$4:$D$10</f>
             </numRef>
           </val>
         </ser>
@@ -537,7 +539,7 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Рис. Профілі DM'!E3</f>
+              <f>'Fig. DM profiles'!E3</f>
             </strRef>
           </tx>
           <spPr>
@@ -555,12 +557,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Профілі DM'!$A$4:$A$10</f>
+              <f>'Fig. DM profiles'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Профілі DM'!$E$4:$E$10</f>
+              <f>'Fig. DM profiles'!$E$4:$E$10</f>
             </numRef>
           </val>
         </ser>
@@ -569,7 +571,7 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Рис. Профілі DM'!F3</f>
+              <f>'Fig. DM profiles'!F3</f>
             </strRef>
           </tx>
           <spPr>
@@ -587,12 +589,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Рис. Профілі DM'!$A$4:$A$10</f>
+              <f>'Fig. DM profiles'!$A$4:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Профілі DM'!$F$4:$F$10</f>
+              <f>'Fig. DM profiles'!$F$4:$F$10</f>
             </numRef>
           </val>
         </ser>
@@ -633,7 +635,7 @@
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="12"/>
+  <style val="11"/>
   <chart>
     <plotArea>
       <barChart>
@@ -644,7 +646,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Рис. Крос-валідація'!B3</f>
+              <f>'Fig. Multi-horizon'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -654,12 +656,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Рис. Крос-валідація'!$A$4:$A$8</f>
+              <f>'Fig. Multi-horizon'!$A$4:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Крос-валідація'!$B$4:$B$8</f>
+              <f>'Fig. Multi-horizon'!$B$4:$B$8</f>
             </numRef>
           </val>
         </ser>
@@ -668,7 +670,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Рис. Крос-валідація'!C3</f>
+              <f>'Fig. Multi-horizon'!C3</f>
             </strRef>
           </tx>
           <spPr>
@@ -678,12 +680,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Рис. Крос-валідація'!$A$4:$A$8</f>
+              <f>'Fig. Multi-horizon'!$A$4:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Крос-валідація'!$C$4:$C$8</f>
+              <f>'Fig. Multi-horizon'!$C$4:$C$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Fig. Multi-horizon'!D3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Fig. Multi-horizon'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Fig. Multi-horizon'!$D$4:$D$8</f>
             </numRef>
           </val>
         </ser>
@@ -706,7 +732,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Рівень</a:t>
+                  <a:t>Scenario</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -733,7 +759,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Частка підприємств</a:t>
+                  <a:t>Δ ADMI</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -755,18 +781,18 @@
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="10"/>
+  <style val="12"/>
   <chart>
     <plotArea>
       <barChart>
-        <barDir val="bar"/>
+        <barDir val="col"/>
         <grouping val="clustered"/>
         <ser>
           <idx val="0"/>
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Рис. Чутливість'!B3</f>
+              <f>'Fig. Cross-validation'!B3</f>
             </strRef>
           </tx>
           <spPr>
@@ -776,12 +802,36 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Рис. Чутливість'!$A$4:$A$10</f>
+              <f>'Fig. Cross-validation'!$A$4:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Рис. Чутливість'!$B$4:$B$10</f>
+              <f>'Fig. Cross-validation'!$B$4:$B$8</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Fig. Cross-validation'!C3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Fig. Cross-validation'!$A$4:$A$8</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Fig. Cross-validation'!$C$4:$C$8</f>
             </numRef>
           </val>
         </ser>
@@ -804,7 +854,7 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Чутливість</a:t>
+                  <a:t>Level</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -831,7 +881,105 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Параметр</a:t>
+                  <a:t>Enterprise share</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <plotArea>
+      <barChart>
+        <barDir val="bar"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Fig. Sensitivity'!B3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Fig. Sensitivity'!$A$4:$A$10</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Fig. Sensitivity'!$B$4:$B$10</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Sensitivity</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Parameter</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -909,6 +1057,33 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>6</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5760000" cy="3960000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
       <col>5</col>
       <colOff>0</colOff>
       <row>2</row>
@@ -932,7 +1107,7 @@
 </wsDr>
 </file>
 
-<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
@@ -1257,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Про звіт імітаційного моделювання ІМ Onion-S</t>
+          <t>Onion-S simulation model report</t>
         </is>
       </c>
     </row>
@@ -1265,67 +1440,67 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Дата запуску</t>
+          <t>Run date</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>2026-04-19 17:32</t>
+          <t>2026-10-10 10:34</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Фінальне α</t>
+          <t>Final α</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>0.8000</t>
+          <t>0.4000</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Фінальне δ</t>
+          <t>Final δ</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>0.3000</t>
+          <t>0.3750</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Середнє α (10 запусків)</t>
+          <t>Mean α (10 runs)</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>0.8000 ± 0.1472</t>
+          <t>0.4167 ± 0.0624</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Середнє δ (10 запусків)</t>
+          <t>Mean δ (10 runs)</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>0.2917 ± 0.0514</t>
+          <t>0.3667 ± 0.0236</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Кількість підприємств</t>
+          <t>Number of enterprises</t>
         </is>
       </c>
       <c r="B8" s="3" t="n">
@@ -1335,7 +1510,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Кількість запусків</t>
+          <t>Number of runs</t>
         </is>
       </c>
       <c r="B9" s="3" t="n">
@@ -1345,7 +1520,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Горизонт (років)</t>
+          <t>Horizon (years)</t>
         </is>
       </c>
       <c r="B10" s="3" t="n">
@@ -1355,7 +1530,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Крок (років)</t>
+          <t>Step (years)</t>
         </is>
       </c>
       <c r="B11" s="3" t="n">
@@ -1365,11 +1540,11 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Час виконання (с)</t>
+          <t>Execution time (s)</t>
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>4.1</v>
+        <v>7.8</v>
       </c>
     </row>
   </sheetData>
@@ -1395,7 +1570,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Матриця переходу Маркова — С-3 Інтеграція (річна)</t>
+          <t>Markov transition matrix — S-3 Integration (annual)</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1578,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>З рівня / На рівень</t>
+          <t>From / To level</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1435,14 +1610,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1 (аналоговий)</t>
+          <t>1 (analog)</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>0.9724770642201835</v>
+        <v>0.9619047619047619</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>0.02752293577981652</v>
+        <v>0.0380952380952381</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>0</v>
@@ -1457,17 +1632,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2 (фрагментарний)</t>
+          <t>2 (fragmented)</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>0.004985480698175461</v>
+        <v>0.004975124378109453</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.9575453533030112</v>
+        <v>0.9697704371543298</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.03746916599881348</v>
+        <v>0.02525443846756067</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>0</v>
@@ -1479,17 +1654,17 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3 (інтегрований)</t>
+          <t>3 (integrated)</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.01433753423086298</v>
+        <v>0.01128146117485137</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.9806873413910276</v>
+        <v>0.9837434144470393</v>
       </c>
       <c r="E6" s="13" t="n">
         <v>0.004975124378109454</v>
@@ -1501,7 +1676,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4 (адаптивний)</t>
+          <t>4 (adaptive)</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -1523,7 +1698,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5 (інтелектуальний)</t>
+          <t>5 (intelligent)</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -1546,7 +1721,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1761,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Стаціонарні розподіли π за сценаріями</t>
+          <t>Stationary distributions π by scenario</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1769,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Сценарій</t>
+          <t>Scenario</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -1626,74 +1801,74 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>0.002794392067903051</v>
+        <v>0.001594279589150746</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.02801880519964406</v>
+        <v>0.02039999457266566</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.3214603367599041</v>
+        <v>0.2172349735093009</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.324666863837362</v>
+        <v>0.3813292604725502</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.3230596021351868</v>
+        <v>0.3794414918563325</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.001365402897294355</v>
+        <v>0.0007653187845361072</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.01955781649206371</v>
+        <v>0.01688367903934125</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.2461332340111008</v>
+        <v>0.2204135644822609</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.367381132538736</v>
+        <v>0.3819140506554906</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.3655624140608052</v>
+        <v>0.3800233870383711</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>0.02005031953936759</v>
+        <v>0.01662074567969127</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.1106901601782897</v>
+        <v>0.1272674240616352</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.289273449630393</v>
+        <v>0.2848981421887378</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.2907126210215824</v>
+        <v>0.2863155458812162</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.2892734496303673</v>
+        <v>0.2848981421887196</v>
       </c>
     </row>
     <row r="7"/>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -1721,7 +1896,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Табл. 2.16. Очікуваний час досягнення рівня (роки)</t>
+          <t>Table 2.16. Expected time to reach level (years)</t>
         </is>
       </c>
     </row>
@@ -1729,22 +1904,22 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Перехід</t>
+          <t>Transition</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
     </row>
@@ -1755,13 +1930,13 @@
         </is>
       </c>
       <c r="B4" s="14" t="n">
-        <v>20</v>
+        <v>15.67</v>
       </c>
       <c r="C4" s="14" t="n">
-        <v>14</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="D4" s="14" t="n">
-        <v>36.33</v>
+        <v>26.25</v>
       </c>
     </row>
     <row r="5">
@@ -1771,13 +1946,13 @@
         </is>
       </c>
       <c r="B5" s="14" t="n">
-        <v>32.84</v>
+        <v>35.93</v>
       </c>
       <c r="C5" s="14" t="n">
-        <v>25.5</v>
+        <v>25.21</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>67.86</v>
+        <v>71.02</v>
       </c>
     </row>
     <row r="6">
@@ -1831,13 +2006,13 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>12.84</v>
+        <v>20.26</v>
       </c>
       <c r="C8" s="14" t="n">
-        <v>11.5</v>
+        <v>16.09</v>
       </c>
       <c r="D8" s="14" t="n">
-        <v>31.52</v>
+        <v>44.77</v>
       </c>
     </row>
     <row r="9">
@@ -1954,7 +2129,7 @@
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32. «–» означає очікуваний час &gt; 100 років.</t>
+          <t>Source: simulation results, 2026-10-10 10:34. «–» means expected time &gt; 100 years.</t>
         </is>
       </c>
     </row>
@@ -1973,6 +2148,175 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Table 2.13. ΔADMI by horizons and scenarios (full data)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>ΔADMI(5)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>ΔADMI(10)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>ΔADMI(15)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Ratio 15/5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Inactivity</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>-0.04491006750001569</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>-0.0819550638382685</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>-0.1207077808555826</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2.7×</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>0.02445386622843781</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0.04603091789592439</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>0.0707505667644997</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2.9×</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S-2 Core</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>0.02888279327365362</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0.05351741781358033</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.07427928409722923</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2.6×</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S-3 Integration</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0.004580956971482919</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.009257916139462974</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.01596510158424347</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>3.5×</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S-4 Market</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>0.02091790493165024</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0.0351000099242515</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.04806228826639991</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2.3×</t>
+        </is>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Source: multi-horizon simulation, 2026-10-10 10:34</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1982,7 +2326,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Табл. 2.14. Крос-валідація SD vs Ланцюги Маркова (рік 5)</t>
+          <t>Table 2.14. Cross-validation SD vs Markov chains (year 5)</t>
         </is>
       </c>
     </row>
@@ -1990,91 +2334,91 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Рівень</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>SD (емпіричний)</t>
+          <t>SD (empirical)</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Маркова (прогноз)</t>
+          <t>Markov (predicted)</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Різниця (в.п.)</t>
+          <t>Difference (pp)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="B5" s="12" t="n">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>0.09469497076907894</v>
+        <v>0.08734316141651759</v>
       </c>
       <c r="D5" s="14" t="n">
-        <v>-0.5</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.3420834422628812</v>
+        <v>0.3386422509449759</v>
       </c>
       <c r="D6" s="14" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.49</v>
+        <v>0.495</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>0.4898830011333368</v>
+        <v>0.4958816263750159</v>
       </c>
       <c r="D7" s="14" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>0.07168739989279725</v>
+        <v>0.07650464848003564</v>
       </c>
       <c r="D8" s="14" t="n">
         <v>0.3</v>
@@ -2083,14 +2427,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="B9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.001651185941905983</v>
+        <v>0.001628312783455024</v>
       </c>
       <c r="D9" s="14" t="n">
         <v>-0.2</v>
@@ -2099,102 +2443,102 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>L1-відхилення</t>
+          <t>L1-deviation</t>
         </is>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0097</v>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Рівень</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>SD (емпіричний)</t>
+          <t>SD (empirical)</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Маркова (прогноз)</t>
+          <t>Markov (predicted)</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Різниця (в.п.)</t>
+          <t>Difference (pp)</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="B14" s="12" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.08503363996300396</v>
+        <v>0.06897360488154322</v>
       </c>
       <c r="D14" s="14" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="B15" s="12" t="n">
-        <v>0.34</v>
+        <v>0.325</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.337065339451363</v>
+        <v>0.3352068473954634</v>
       </c>
       <c r="D15" s="14" t="n">
-        <v>0.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="B16" s="12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.4996480375285168</v>
+        <v>0.5175482504979727</v>
       </c>
       <c r="D16" s="14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="B17" s="12" t="n">
         <v>0.08</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.0765580658723468</v>
+        <v>0.07664341397183824</v>
       </c>
       <c r="D17" s="14" t="n">
         <v>0.3</v>
@@ -2203,14 +2547,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="B18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.00169491718476937</v>
+        <v>0.001627883253182017</v>
       </c>
       <c r="D18" s="14" t="n">
         <v>-0.2</v>
@@ -2219,118 +2563,118 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>L1-відхилення</t>
+          <t>L1-deviation</t>
         </is>
       </c>
       <c r="D19" s="10" t="n">
-        <v>0.0135</v>
+        <v>0.0316</v>
       </c>
     </row>
     <row r="20"/>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Рівень</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>SD (емпіричний)</t>
+          <t>SD (empirical)</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Маркова (прогноз)</t>
+          <t>Markov (predicted)</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Різниця (в.п.)</t>
+          <t>Difference (pp)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="B23" s="12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>0.1067430536561393</v>
+        <v>0.0997667621093043</v>
       </c>
       <c r="D23" s="14" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>0.43556978315109</v>
+        <v>0.3892677845654403</v>
       </c>
       <c r="D24" s="14" t="n">
-        <v>0.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>0.395</v>
+        <v>0.45</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>0.3855528659697847</v>
+        <v>0.4417805821624474</v>
       </c>
       <c r="D25" s="14" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="B26" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>0.07048958477514559</v>
+        <v>0.06763933329957224</v>
       </c>
       <c r="D26" s="14" t="n">
-        <v>-0.5</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="B27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>0.001644712447841008</v>
+        <v>0.001545537863235981</v>
       </c>
       <c r="D27" s="14" t="n">
         <v>-0.2</v>
@@ -2339,18 +2683,18 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>L1-відхилення</t>
+          <t>L1-deviation</t>
         </is>
       </c>
       <c r="D28" s="10" t="n">
-        <v>0.0278</v>
+        <v>0.0379</v>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2707,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2378,7 +2722,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Табл. 2.17. Аналіз чутливості (OAT ±20%)</t>
+          <t>Table 2.17. Sensitivity analysis (OAT ±20%)</t>
         </is>
       </c>
     </row>
@@ -2386,142 +2730,142 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Параметр</t>
+          <t>Parameter</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Базове</t>
+          <t>Base</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Метрика @ -20%</t>
+          <t>Metric @ -20%</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Метрика @ +20%</t>
+          <t>Metric @ +20%</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>Чутливість</t>
+          <t>Sensitivity</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>budget_total</t>
+          <t>investment_efficiency</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.4012991442286465</v>
+        <v>0.3904847255099163</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.4294781717794052</v>
+        <v>0.4159028067585442</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.1695100462545814</v>
+        <v>0.1576426038754329</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>investment_efficiency</t>
+          <t>budget_total</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.4012449124160958</v>
+        <v>0.3905520665756049</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.429376390783665</v>
+        <v>0.4155152507771762</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.1692240156515983</v>
+        <v>0.1548213384033541</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>alpha</t>
+          <t>absorptive_saturation</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>0.8000000000000003</v>
+        <v>0.4</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.5666659035985301</v>
+        <v>0.407440115586207</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.5456030024260928</v>
+        <v>0.3992792078495794</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.0948036993752349</v>
+        <v>0.05061384189487465</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>delta</t>
+          <t>alpha</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.5564386557778337</v>
+        <v>0.5708734968221356</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.5462899088017663</v>
+        <v>0.5805056704041955</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.04567930834777231</v>
+        <v>0.04138681021722641</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>absorptive_saturation</t>
+          <t>integration_power</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.4180939803928308</v>
+        <v>0.4056956094580452</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.4115257163569755</v>
+        <v>0.4013356857121119</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.0395111839301268</v>
+        <v>0.02704018943382517</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>integration_power</t>
+          <t>delta</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>0.5</v>
+        <v>0.3749999999999999</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.4173929330427671</v>
+        <v>0.574763288010258</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.4132483641818597</v>
+        <v>0.5791183725483913</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.0249315224967303</v>
+        <v>0.01871260476403834</v>
       </c>
     </row>
     <row r="10">
@@ -2534,20 +2878,20 @@
         <v>0.025</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.415600471870313</v>
+        <v>0.4032546647709221</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.4155964679226638</v>
+        <v>0.4032170323636858</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>2.408562005863418e-05</v>
+        <v>0.0002333956921769153</v>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2904,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2575,7 +2919,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Рис. 2.3.2. Траєкторії ADMI за сценаріями (5 років)</t>
+          <t>Fig. 2.3.2. ADMI trajectories by scenario (5 years)</t>
         </is>
       </c>
     </row>
@@ -2583,32 +2927,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Бездіяльність</t>
+          <t>Inactivity</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>С-4 Ринкова</t>
+          <t>S-4 Market</t>
         </is>
       </c>
     </row>
@@ -2617,19 +2961,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="10" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
     </row>
     <row r="5">
@@ -2637,19 +2981,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.3605308704575152</v>
+        <v>0.3837076415283363</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.3758039615378311</v>
+        <v>0.3976494647264437</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.3767424733323877</v>
+        <v>0.3985216267383477</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.3710412993769363</v>
+        <v>0.3935116009518732</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.3739972687997688</v>
+        <v>0.395671893848896</v>
       </c>
     </row>
     <row r="6">
@@ -2657,19 +3001,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="10" t="n">
-        <v>0.3516656382687368</v>
+        <v>0.3745631699060188</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.3820465038004179</v>
+        <v>0.4023781152920212</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.3837690792431166</v>
+        <v>0.4040848369825167</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.3728300049489147</v>
+        <v>0.3940344953936439</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.3782624854318128</v>
+        <v>0.3981351490921974</v>
       </c>
     </row>
     <row r="7">
@@ -2677,19 +3021,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.3431129664481376</v>
+        <v>0.3655382118789667</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.3884015171350855</v>
+        <v>0.4070330924140632</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.3904761192158368</v>
+        <v>0.4095844130309628</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.3746367340497398</v>
+        <v>0.3947363994052702</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.3860629747156927</v>
+        <v>0.4037877776660765</v>
       </c>
     </row>
     <row r="8">
@@ -2697,19 +3041,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="10" t="n">
-        <v>0.3345089541626757</v>
+        <v>0.3568102309118118</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.3945549039292197</v>
+        <v>0.4119768772614267</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.3968316438164831</v>
+        <v>0.415138635171817</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.3765285802584857</v>
+        <v>0.3957377174415083</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.3933256729694861</v>
+        <v>0.4089497134662814</v>
       </c>
     </row>
     <row r="9">
@@ -2717,26 +3061,26 @@
         <v>5</v>
       </c>
       <c r="B9" s="10" t="n">
-        <v>0.3262024560229315</v>
+        <v>0.3483121580984781</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.4007752089825164</v>
+        <v>0.4169906873110233</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.4028112546500164</v>
+        <v>0.4205541091830805</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.3786041524378011</v>
+        <v>0.3970403666874905</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.39985861456448</v>
+        <v>0.4137630604599687</v>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -2750,7 +3094,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2765,7 +3109,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Рис. 2.3.3. Профілі DM за сценаріями (рік 5, radar)</t>
+          <t>Fig. 2.3.3. DM profiles by scenario (year 5, radar)</t>
         </is>
       </c>
     </row>
@@ -2773,32 +3117,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Компонент</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Бездіяльність</t>
+          <t>Inactivity</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>С-4 Ринкова</t>
+          <t>S-4 Market</t>
         </is>
       </c>
     </row>
@@ -2809,19 +3153,19 @@
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>0.4003850593081164</v>
+        <v>0.4159146594162255</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.4842136850074039</v>
+        <v>0.4968859800188802</v>
       </c>
       <c r="D4" s="10" t="n">
-        <v>0.57170371246795</v>
+        <v>0.582512231692296</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>0.4624327223517494</v>
+        <v>0.4755940260484063</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>0.4333798667041744</v>
+        <v>0.4480958198502777</v>
       </c>
     </row>
     <row r="5">
@@ -2831,19 +3175,19 @@
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.3911126670498661</v>
+        <v>0.3902389878792183</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.4493725372515353</v>
+        <v>0.4502101137430297</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>0.4829393532137277</v>
+        <v>0.4841467443659926</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>0.4324864432645233</v>
+        <v>0.4340990411539536</v>
       </c>
       <c r="F5" s="10" t="n">
-        <v>0.4117255582189136</v>
+        <v>0.4126432449161025</v>
       </c>
     </row>
     <row r="6">
@@ -2853,19 +3197,19 @@
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>0.3665773173810934</v>
+        <v>0.3685102850047615</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.4267112843642416</v>
+        <v>0.4295727316853429</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>0.4103036258504539</v>
+        <v>0.413252858631375</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.4092496292418277</v>
+        <v>0.4115355470476794</v>
       </c>
       <c r="F6" s="10" t="n">
-        <v>0.4075658829903521</v>
+        <v>0.4095638780235318</v>
       </c>
     </row>
     <row r="7">
@@ -2875,19 +3219,19 @@
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.3469901972404624</v>
+        <v>0.3550202851629872</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.4062636269387966</v>
+        <v>0.4140977691180214</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>0.3683930647241552</v>
+        <v>0.376296472675313</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.3875163407387333</v>
+        <v>0.3965975742389583</v>
       </c>
       <c r="F7" s="10" t="n">
-        <v>0.4043798335838054</v>
+        <v>0.4129529170725926</v>
       </c>
     </row>
     <row r="8">
@@ -2897,19 +3241,19 @@
         </is>
       </c>
       <c r="B8" s="10" t="n">
-        <v>0.3254691491272174</v>
+        <v>0.3611761483808724</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.3826469694046506</v>
+        <v>0.4181873262399166</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0.3459456188065548</v>
+        <v>0.381012794970687</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>0.3657360886346943</v>
+        <v>0.4008569952025799</v>
       </c>
       <c r="F8" s="10" t="n">
-        <v>0.4666998622414589</v>
+        <v>0.4998499580705074</v>
       </c>
     </row>
     <row r="9">
@@ -2919,19 +3263,19 @@
         </is>
       </c>
       <c r="B9" s="10" t="n">
-        <v>0.3256617836405353</v>
+        <v>0.3195204382239025</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>0.4193691077550387</v>
+        <v>0.4126425952732784</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>0.4187899659179348</v>
+        <v>0.4112862086872531</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>0.5454526062282885</v>
+        <v>0.5370930006514132</v>
       </c>
       <c r="F9" s="10" t="n">
-        <v>0.4471232159913421</v>
+        <v>0.4397309591835246</v>
       </c>
     </row>
     <row r="10">
@@ -2941,26 +3285,26 @@
         </is>
       </c>
       <c r="B10" s="10" t="n">
-        <v>0.361657092410864</v>
+        <v>0.3850094263382479</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>0.4312003057485995</v>
+        <v>0.4532678327211507</v>
       </c>
       <c r="D10" s="10" t="n">
-        <v>0.3990470136124556</v>
+        <v>0.4215687288327747</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>0.4308980345119556</v>
+        <v>0.4532542955596361</v>
       </c>
       <c r="F10" s="10" t="n">
-        <v>0.4606806143340989</v>
+        <v>0.4825207110735795</v>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -2974,7 +3318,147 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fig. 2.3.4. ΔADMI by horizons (5/10/15 years)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Scenario</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>5 years</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>10 years</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>15 years</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Inactivity</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="n">
+        <v>-0.04491006750001569</v>
+      </c>
+      <c r="C4" s="10" t="n">
+        <v>-0.0819550638382685</v>
+      </c>
+      <c r="D4" s="10" t="n">
+        <v>-0.1207077808555826</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Uniform</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>0.02445386622843781</v>
+      </c>
+      <c r="C5" s="10" t="n">
+        <v>0.04603091789592439</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>0.0707505667644997</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>S-2 Core</t>
+        </is>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>0.02888279327365362</v>
+      </c>
+      <c r="C6" s="10" t="n">
+        <v>0.05351741781358033</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>0.07427928409722923</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>S-3 Integration</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0.004580956971482919</v>
+      </c>
+      <c r="C7" s="10" t="n">
+        <v>0.009257916139462974</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>0.01596510158424347</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>S-4 Market</t>
+        </is>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>0.02091790493165024</v>
+      </c>
+      <c r="C8" s="10" t="n">
+        <v>0.0351000099242515</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>0.04806228826639991</v>
+      </c>
+    </row>
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Source: multi-horizon simulation, 2026-10-10 10:34</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A1:E1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2989,7 +3473,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Рис. 2.3.5. Крос-валідація SD vs Маркова (Рівномірна, рік 5)</t>
+          <t>Fig. 2.3.5. Cross-validation SD vs Markov (Uniform, year 5)</t>
         </is>
       </c>
     </row>
@@ -2997,90 +3481,90 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Рівень</t>
+          <t>Level</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>SD (емпіричний)</t>
+          <t>SD (empirical)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Маркова (прогноз)</t>
+          <t>Markov (predicted)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
-        <v>0.09</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>0.09469497076907894</v>
+        <v>0.08734316141651759</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="B5" s="10" t="n">
-        <v>0.345</v>
+        <v>0.34</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>0.3420834422628812</v>
+        <v>0.3386422509449759</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
-        <v>0.49</v>
+        <v>0.495</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>0.4898830011333368</v>
+        <v>0.4958816263750159</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
-        <v>0.075</v>
+        <v>0.08</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>0.07168739989279725</v>
+        <v>0.07650464848003564</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
         <v>0</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>0.001651185941905983</v>
+        <v>0.001628312783455024</v>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32. L1-відхилення: 0.0127</t>
+          <t>Source: simulation results, 2026-10-10 10:34. L1-deviation: 0.0097</t>
         </is>
       </c>
     </row>
@@ -3088,126 +3572,6 @@
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A10:D10"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Рис. 2.3.7. Аналіз чутливості (tornado, OAT ±20%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Параметр</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Чутливість</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>budget_total</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>0.1695100462545814</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>investment_efficiency</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="n">
-        <v>0.1692240156515983</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>alpha</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>0.0948036993752349</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>delta</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>0.04567930834777231</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>absorptive_saturation</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>0.0395111839301268</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>integration_power</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>0.0249315224967303</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>base_depreciation</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>2.408562005863418e-05</v>
-      </c>
-    </row>
-    <row r="11"/>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A12:C12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -3229,7 +3593,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Табл. 2.10. Калібрація α та δ (10 запусків × 1000 підприємств)</t>
+          <t>Table 2.10. Calibration of α and δ (10 runs × 1000 enterprises)</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3601,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Запуск</t>
+          <t>Run</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -3284,22 +3648,22 @@
         <v>42</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.6500000000000001</v>
+        <v>0.3500000000000001</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.225</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.5809360053961135</v>
+        <v>0.5814774715780671</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.9285922148053701</v>
+        <v>0.9534388359708993</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.6983303982465514</v>
+        <v>0.7070064572990244</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="5">
@@ -3310,22 +3674,22 @@
         <v>179</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.7500000000000002</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>0.35</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.5695914828080761</v>
+        <v>0.5795257662344822</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.9088367209180229</v>
+        <v>0.9439795994899872</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.6868559814695566</v>
+        <v>0.6931130881282909</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="6">
@@ -3336,19 +3700,19 @@
         <v>316</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1</v>
+        <v>0.5000000000000001</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.35</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.5791816601113197</v>
+        <v>0.5714064972877789</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.9081347033675842</v>
+        <v>0.9258726468161704</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.7197592625476199</v>
+        <v>0.6701914618710357</v>
       </c>
       <c r="H6" s="5" t="n">
         <v>0</v>
@@ -3357,34 +3721,34 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Середнє</t>
+          <t>Mean</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.8000000000000002</v>
+        <v>0.4166666666666668</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2916666666666666</v>
+        <v>0.3666666666666666</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Ст. відхилення</t>
+          <t>StDev</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1471960144387975</v>
+        <v>0.06236095644623237</v>
       </c>
       <c r="D8" t="n">
-        <v>0.05137011669140813</v>
+        <v>0.02357022603955155</v>
       </c>
     </row>
     <row r="9"/>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -3394,6 +3758,126 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="30" customWidth="1" min="1" max="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fig. 2.3.7. Sensitivity analysis (tornado, OAT ±20%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Sensitivity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>investment_efficiency</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>0.1576426038754329</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>budget_total</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>0.1548213384033541</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>absorptive_saturation</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="n">
+        <v>0.05061384189487465</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>alpha</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>0.04138681021722641</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>integration_power</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>0.02704018943382517</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>delta</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="n">
+        <v>0.01871260476403834</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>base_depreciation</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>0.0002333956921769153</v>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A12:C12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3412,7 +3896,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Теплова карта J(α, δ) — середнє по 10 запусках</t>
+          <t>Heatmap J(α, δ) — averaged over 10 runs</t>
         </is>
       </c>
     </row>
@@ -3468,43 +3952,43 @@
         <v>0.1</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.5210270022858553</v>
+        <v>0.5303821200294899</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.5229490003358066</v>
+        <v>0.5304748693119361</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.5230087057679648</v>
+        <v>0.5366771174263514</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.5250495268491956</v>
+        <v>0.5368084882989423</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.5254261804447303</v>
+        <v>0.5350265325330293</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.5256945053631318</v>
+        <v>0.5331968946456099</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.5260458495488671</v>
+        <v>0.5353743017198185</v>
       </c>
       <c r="I4" s="5" t="n">
-        <v>0.5269655638833584</v>
+        <v>0.5405965409879822</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.5291336138780695</v>
+        <v>0.5387734747805338</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.531576545410648</v>
+        <v>0.5409155631233834</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.531849876963899</v>
+        <v>0.5417454971150991</v>
       </c>
       <c r="M4" s="5" t="n">
-        <v>0.5322956866032972</v>
+        <v>0.5439377710343016</v>
       </c>
       <c r="N4" s="5" t="n">
-        <v>0.5324525897609532</v>
+        <v>0.5415512202937548</v>
       </c>
     </row>
     <row r="5">
@@ -3512,43 +3996,43 @@
         <v>0.15</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.5209378000557996</v>
+        <v>0.5323053181094419</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.5249983055079582</v>
+        <v>0.5382162628467744</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.5273015572684471</v>
+        <v>0.5388095271078938</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.5253979509164362</v>
+        <v>0.538785926517879</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.5299480111176299</v>
+        <v>0.5409908921345788</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.5341506407672205</v>
+        <v>0.5438607138438986</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.5390929333203458</v>
+        <v>0.5447825222825022</v>
       </c>
       <c r="I5" s="5" t="n">
-        <v>0.539351971247215</v>
+        <v>0.549076280384681</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.5415296952474979</v>
+        <v>0.547458065362062</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.5419358319145128</v>
+        <v>0.5518653142502216</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.544815336500069</v>
+        <v>0.5544783317596854</v>
       </c>
       <c r="M5" s="5" t="n">
-        <v>0.5451642519443092</v>
+        <v>0.556739699418582</v>
       </c>
       <c r="N5" s="5" t="n">
-        <v>0.5453021771018386</v>
+        <v>0.55755710589904</v>
       </c>
     </row>
     <row r="6">
@@ -3556,43 +4040,43 @@
         <v>0.2</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.5230613070829977</v>
+        <v>0.5363160653418367</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.5273161576334562</v>
+        <v>0.5382086302442785</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.5272113777136936</v>
+        <v>0.5386511231477947</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.5317082518663944</v>
+        <v>0.5348860117080793</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.5383149272471165</v>
+        <v>0.5415712358947726</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.5448011660134756</v>
+        <v>0.548410378946504</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.5450497993947454</v>
+        <v>0.5528093195097322</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>0.5495868158250491</v>
+        <v>0.5509686298128919</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.5498480470436983</v>
+        <v>0.5578422940005978</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0.5488611184654436</v>
+        <v>0.5608065841598827</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.5490898175595832</v>
+        <v>0.5599335577423644</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>0.5516048069217021</v>
+        <v>0.5621710438910298</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>0.5517885215378108</v>
+        <v>0.562617702185446</v>
       </c>
     </row>
     <row r="7">
@@ -3600,43 +4084,43 @@
         <v>0.2500000000000001</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.5269521043529294</v>
+        <v>0.5364050351544011</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.5272157751845988</v>
+        <v>0.5382468699832531</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.5334075333008724</v>
+        <v>0.5365050773501775</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.5399010384475068</v>
+        <v>0.5448203273790664</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.546173778673074</v>
+        <v>0.5499005002319509</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.5506267235935973</v>
+        <v>0.5562096197265965</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.550876347612307</v>
+        <v>0.5568724324312139</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>0.5499296756235067</v>
+        <v>0.5621750432010363</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>0.5523499175462216</v>
+        <v>0.5612024992984243</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.5525383432961704</v>
+        <v>0.5642905041774167</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.5529885274935782</v>
+        <v>0.5648179761197074</v>
       </c>
       <c r="M7" s="5" t="n">
-        <v>0.5549096888530307</v>
+        <v>0.5648100235710581</v>
       </c>
       <c r="N7" s="5" t="n">
-        <v>0.5549528857095193</v>
+        <v>0.5656226013995798</v>
       </c>
     </row>
     <row r="8">
@@ -3644,43 +4128,43 @@
         <v>0.3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.5270819690685794</v>
+        <v>0.5362834321143252</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.5292515787187188</v>
+        <v>0.5360638654081388</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.5373606929075377</v>
+        <v>0.5386779270561065</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.5457905594690114</v>
+        <v>0.5496529646743552</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.5498964979804123</v>
+        <v>0.5538492263950499</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.5484356501037775</v>
+        <v>0.5583447632650864</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.5518344796342803</v>
+        <v>0.5631608194652232</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>0.5515888188395426</v>
+        <v>0.5649528143662411</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.5538096478012012</v>
+        <v>0.5659499145963337</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.5575320691399369</v>
+        <v>0.5667712198098677</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.5583856695112354</v>
+        <v>0.5680314885761499</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>0.5586837046453978</v>
+        <v>0.5680233440558223</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>0.557163513464794</v>
+        <v>0.5681643923814025</v>
       </c>
     </row>
     <row r="9">
@@ -3688,43 +4172,43 @@
         <v>0.3500000000000001</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.5273513785746835</v>
+        <v>0.5361294282642289</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.533386132765859</v>
+        <v>0.5365117997137477</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.5434599845737131</v>
+        <v>0.5448360457599839</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.5515753637127</v>
+        <v>0.5557799398722457</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.5478550373469007</v>
+        <v>0.5576906493120229</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.5530539804438717</v>
+        <v>0.5603405316565785</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.5552314229239164</v>
+        <v>0.5638151862131627</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0.5553878647551308</v>
+        <v>0.5674562271089315</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.5567750052696872</v>
+        <v>0.5683458255488629</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>0.5571342744762747</v>
+        <v>0.5717690543863396</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>0.555496675184139</v>
+        <v>0.571916481433126</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>0.5564319222457722</v>
+        <v>0.5714756406941538</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>0.5555403092613169</v>
+        <v>0.5697561966193071</v>
       </c>
     </row>
     <row r="10">
@@ -3732,43 +4216,43 @@
         <v>0.4000000000000001</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.531292977114647</v>
+        <v>0.5359768244491335</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.5373141277286848</v>
+        <v>0.5383689987827561</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.5471091758034938</v>
+        <v>0.5507792507517566</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.5474095315997139</v>
+        <v>0.5577127963853686</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.5542326076540757</v>
+        <v>0.5594923792719579</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.5523415669608269</v>
+        <v>0.565260479914436</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.5535372851779184</v>
+        <v>0.5665614012908334</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0.5538781345413594</v>
+        <v>0.5674504031633033</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>0.5524573857951912</v>
+        <v>0.5727345280756355</v>
       </c>
       <c r="K10" s="5" t="n">
-        <v>0.5524178819422562</v>
+        <v>0.5729032561024926</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>0.5554467093948068</v>
+        <v>0.5733985662555915</v>
       </c>
       <c r="M10" s="5" t="n">
-        <v>0.5578784287231294</v>
+        <v>0.5714172462750466</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>0.5565240976020905</v>
+        <v>0.5702657113310799</v>
       </c>
     </row>
     <row r="11">
@@ -3776,43 +4260,43 @@
         <v>0.4500000000000001</v>
       </c>
       <c r="B11" s="5" t="n">
-        <v>0.531160173794564</v>
+        <v>0.5341416673531875</v>
       </c>
       <c r="C11" s="5" t="n">
-        <v>0.5433187921501074</v>
+        <v>0.5400991920375875</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>0.5488171685033113</v>
+        <v>0.5551340829746283</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.5516568130988748</v>
+        <v>0.5545836826136564</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>0.5522167256521778</v>
+        <v>0.5621508188965122</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.5554135995548287</v>
+        <v>0.5650964881143169</v>
       </c>
       <c r="H11" s="5" t="n">
-        <v>0.5531875854877417</v>
+        <v>0.5666691035151139</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0.5515256167776879</v>
+        <v>0.569807800408796</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>0.553649652744313</v>
+        <v>0.5699906332869223</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>0.5591012527997458</v>
+        <v>0.5707310430914926</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>0.5588972041925161</v>
+        <v>0.5696842432384358</v>
       </c>
       <c r="M11" s="5" t="n">
-        <v>0.5580889625389948</v>
+        <v>0.5712336615193809</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>0.5587804956253679</v>
+        <v>0.571910326375953</v>
       </c>
     </row>
     <row r="12">
@@ -3820,43 +4304,43 @@
         <v>0.5000000000000001</v>
       </c>
       <c r="B12" s="5" t="n">
-        <v>0.5311917772236813</v>
+        <v>0.5339242619180514</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0.5471389726280703</v>
+        <v>0.5443798145689832</v>
       </c>
       <c r="D12" s="5" t="n">
-        <v>0.5507826504159289</v>
+        <v>0.5572115256618905</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>0.5535183337358562</v>
+        <v>0.5533459995342338</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.5538337055677122</v>
+        <v>0.5645084673442256</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.5545004223352263</v>
+        <v>0.5676282209777841</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.5507110107270019</v>
+        <v>0.5691650528279346</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0.5566285474041222</v>
+        <v>0.5688909824345408</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0.5610676801157036</v>
+        <v>0.5696530968916048</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0.5639898331254284</v>
+        <v>0.5700704430386783</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>0.5651054819336566</v>
+        <v>0.570398531074977</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>0.5639884482927539</v>
+        <v>0.5712287729557667</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>0.5637617343596256</v>
+        <v>0.5690568053314856</v>
       </c>
     </row>
     <row r="13">
@@ -3864,43 +4348,43 @@
         <v>0.5500000000000002</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.5330261730835778</v>
+        <v>0.5362241521033767</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.5488707659229027</v>
+        <v>0.5469044105787603</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.5509540206835613</v>
+        <v>0.5545758824186516</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.5496900132492906</v>
+        <v>0.5534768819475834</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.5550553475477049</v>
+        <v>0.5643190622498359</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.5517288808100161</v>
+        <v>0.5656663414179303</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>0.5557674589449269</v>
+        <v>0.568185081382136</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>0.5620718745055369</v>
+        <v>0.5683602175196599</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>0.5630353497828658</v>
+        <v>0.5688811312022274</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>0.5641175288361552</v>
+        <v>0.5684907537386138</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>0.5650388814892473</v>
+        <v>0.5688457548591888</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>0.5654386049839508</v>
+        <v>0.5680088644687992</v>
       </c>
       <c r="N13" s="5" t="n">
-        <v>0.5674240621009313</v>
+        <v>0.5664899714055557</v>
       </c>
     </row>
     <row r="14">
@@ -3908,43 +4392,43 @@
         <v>0.6000000000000002</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.5330921400341159</v>
+        <v>0.5380757483932838</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.5487725673882835</v>
+        <v>0.5506014030035709</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.5526886598430015</v>
+        <v>0.5524801619938323</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.5536300709813916</v>
+        <v>0.5575044230423093</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.552266817017668</v>
+        <v>0.5642510458752796</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.5533321828140547</v>
+        <v>0.5655691003720204</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.5653461149261728</v>
+        <v>0.5675765854170831</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>0.5652460583154844</v>
+        <v>0.5687131252184143</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.5674922598882829</v>
+        <v>0.5690088248186816</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>0.5670153419894938</v>
+        <v>0.5684170190151147</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>0.5667587621434861</v>
+        <v>0.5684954972268151</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>0.565899195034177</v>
+        <v>0.5660651999792176</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>0.5672351596894539</v>
+        <v>0.5656496028128435</v>
       </c>
     </row>
     <row r="15">
@@ -3952,43 +4436,43 @@
         <v>0.6500000000000001</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.5389804842755563</v>
+        <v>0.5379485452132043</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.551016577017661</v>
+        <v>0.5499516686508543</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.5525911483456701</v>
+        <v>0.5545212622530742</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.5564494705866442</v>
+        <v>0.5595243464548267</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.5533127471038423</v>
+        <v>0.5638314674320772</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.5584760083050043</v>
+        <v>0.5650036144399557</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.5640130432281532</v>
+        <v>0.5661126383369414</v>
       </c>
       <c r="I15" s="5" t="n">
-        <v>0.5684934317377824</v>
+        <v>0.5670631088167158</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>0.5686767806613704</v>
+        <v>0.5652026323793945</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>0.5685299459470848</v>
+        <v>0.5674186216873622</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>0.5677268591245951</v>
+        <v>0.5624552236766259</v>
       </c>
       <c r="M15" s="5" t="n">
-        <v>0.5673126518290225</v>
+        <v>0.5602405830327668</v>
       </c>
       <c r="N15" s="5" t="n">
-        <v>0.5684110387004147</v>
+        <v>0.5594420544923115</v>
       </c>
     </row>
     <row r="16">
@@ -3996,43 +4480,43 @@
         <v>0.7000000000000002</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.543070868680043</v>
+        <v>0.5377613405330873</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.5508090706527176</v>
+        <v>0.5496184603206461</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.5505052139614339</v>
+        <v>0.556821839335648</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.5537002571712585</v>
+        <v>0.5657773184608472</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.5552415361810944</v>
+        <v>0.5643122022051091</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.5659785492383415</v>
+        <v>0.5623344840564306</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.5657553320127503</v>
+        <v>0.5610892846223994</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.5680835176315148</v>
+        <v>0.5610735410342088</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>0.5682897745682643</v>
+        <v>0.5664748557946778</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>0.5678498344805409</v>
+        <v>0.5642230143693551</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>0.5668587361222358</v>
+        <v>0.5626142083943285</v>
       </c>
       <c r="M16" s="5" t="n">
-        <v>0.5680124958622054</v>
+        <v>0.5590281881235492</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>0.565099431251884</v>
+        <v>0.5572752759054564</v>
       </c>
     </row>
     <row r="17">
@@ -4040,43 +4524,43 @@
         <v>0.7500000000000002</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>0.5448808639299243</v>
+        <v>0.5420951831996873</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.5526977451643189</v>
+        <v>0.5499330884401167</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.5561640895678717</v>
+        <v>0.5565517007082375</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.5569684494785401</v>
+        <v>0.563280333168627</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.5616890390657816</v>
+        <v>0.5621543828643479</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.5652212062161172</v>
+        <v>0.5628444859928409</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.566221817770877</v>
+        <v>0.5634669762900163</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.5678113114494338</v>
+        <v>0.5637477020065963</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>0.5676881870249678</v>
+        <v>0.5639132089638833</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>0.5657114204172337</v>
+        <v>0.5620148486112891</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>0.5698335884399683</v>
+        <v>0.5626176070980434</v>
       </c>
       <c r="M17" s="5" t="n">
-        <v>0.5703313198724517</v>
+        <v>0.5590421855592195</v>
       </c>
       <c r="N17" s="5" t="n">
-        <v>0.5636798981954346</v>
+        <v>0.5591279974577807</v>
       </c>
     </row>
     <row r="18">
@@ -4084,43 +4568,43 @@
         <v>0.8000000000000003</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>0.5467656143059378</v>
+        <v>0.5440165812346383</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.5525027095304827</v>
+        <v>0.5536118804099158</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.5561883964160774</v>
+        <v>0.5591260265531018</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.5563494548701572</v>
+        <v>0.564717461363908</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.5634775490869969</v>
+        <v>0.5615155784663949</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.5652940801025662</v>
+        <v>0.5622912151610742</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.5659080053381841</v>
+        <v>0.563325874986723</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.5709541905672945</v>
+        <v>0.5640565616558909</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>0.5704455147765632</v>
+        <v>0.5656292027987587</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>0.5712999994410016</v>
+        <v>0.5642472354036046</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>0.5706378734840549</v>
+        <v>0.5644728919333396</v>
       </c>
       <c r="M18" s="5" t="n">
-        <v>0.5669431998461495</v>
+        <v>0.5611731862853288</v>
       </c>
       <c r="N18" s="5" t="n">
-        <v>0.5595812953335116</v>
+        <v>0.5569784856636322</v>
       </c>
     </row>
     <row r="19">
@@ -4128,43 +4612,43 @@
         <v>0.8500000000000003</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0.5492146579026592</v>
+        <v>0.5457394448970072</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.5501657011052721</v>
+        <v>0.5532735379189387</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.5556736172779725</v>
+        <v>0.559098318067986</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.5581369525482198</v>
+        <v>0.5624167262591113</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.5665635601734705</v>
+        <v>0.5633947928002603</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.5693160101160326</v>
+        <v>0.5659714995722063</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.5701501590939134</v>
+        <v>0.5660583383396006</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>0.5699900505822358</v>
+        <v>0.5676631329228026</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>0.5690183847856081</v>
+        <v>0.5662148365659498</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>0.5704717848270322</v>
+        <v>0.5650976484293648</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>0.5681555822400667</v>
+        <v>0.5629482510948773</v>
       </c>
       <c r="M19" s="5" t="n">
-        <v>0.5612602817524273</v>
+        <v>0.558663388563211</v>
       </c>
       <c r="N19" s="5" t="n">
-        <v>0.5588923090617099</v>
+        <v>0.554358334576742</v>
       </c>
     </row>
     <row r="20">
@@ -4172,43 +4656,43 @@
         <v>0.9000000000000002</v>
       </c>
       <c r="B20" s="5" t="n">
-        <v>0.5490942948808961</v>
+        <v>0.5475994413969197</v>
       </c>
       <c r="C20" s="5" t="n">
-        <v>0.5503030822722826</v>
+        <v>0.5572904523145866</v>
       </c>
       <c r="D20" s="5" t="n">
-        <v>0.5592469681605264</v>
+        <v>0.5586199448581061</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>0.565520512569977</v>
+        <v>0.5662914300250845</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>0.567128503188326</v>
+        <v>0.5672144550597064</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.5686047126261999</v>
+        <v>0.5677918416496567</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>0.569120851379571</v>
+        <v>0.5666413799857906</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>0.568740151420852</v>
+        <v>0.5663611396621268</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>0.5703179165246177</v>
+        <v>0.5641045358962197</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>0.5689642891271677</v>
+        <v>0.5641741894985516</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>0.5638754830564215</v>
+        <v>0.5603159639754627</v>
       </c>
       <c r="M20" s="5" t="n">
-        <v>0.5594885887398374</v>
+        <v>0.5554876520362471</v>
       </c>
       <c r="N20" s="5" t="n">
-        <v>0.5546672571086876</v>
+        <v>0.5520507735531813</v>
       </c>
     </row>
     <row r="21">
@@ -4216,43 +4700,43 @@
         <v>0.9500000000000003</v>
       </c>
       <c r="B21" s="5" t="n">
-        <v>0.5507908872957065</v>
+        <v>0.5473910361867895</v>
       </c>
       <c r="C21" s="5" t="n">
-        <v>0.5527406133020302</v>
+        <v>0.5579343617794487</v>
       </c>
       <c r="D21" s="5" t="n">
-        <v>0.5566464191143855</v>
+        <v>0.5582883326500055</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>0.5653152693749658</v>
+        <v>0.5684391157027519</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>0.5682966335484704</v>
+        <v>0.5675541049216096</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.5684411682446783</v>
+        <v>0.5674113368665905</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>0.5683194121079809</v>
+        <v>0.5663777608263549</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>0.5670942922599328</v>
+        <v>0.5648326769460669</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>0.5695441171877537</v>
+        <v>0.5633487229683147</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>0.5666140611795408</v>
+        <v>0.5623340761417044</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>0.5634042631317991</v>
+        <v>0.5576242328409385</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>0.560127245225316</v>
+        <v>0.5533434942174514</v>
       </c>
       <c r="N21" s="5" t="n">
-        <v>0.5526695922651559</v>
+        <v>0.5531148845622326</v>
       </c>
     </row>
     <row r="22">
@@ -4260,50 +4744,50 @@
         <v>1</v>
       </c>
       <c r="B22" s="5" t="n">
-        <v>0.5525911984481292</v>
+        <v>0.5471908311816643</v>
       </c>
       <c r="C22" s="5" t="n">
-        <v>0.5532165550056323</v>
+        <v>0.5600678601243626</v>
       </c>
       <c r="D22" s="5" t="n">
-        <v>0.5600038030489838</v>
+        <v>0.5599177473267108</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>0.5644231205139589</v>
+        <v>0.5657347245507047</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>0.5678925262599314</v>
+        <v>0.566498403073285</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.5674584759693208</v>
+        <v>0.5661955274311153</v>
       </c>
       <c r="H22" s="5" t="n">
-        <v>0.5674956398182959</v>
+        <v>0.5650943762315296</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>0.5695818141925023</v>
+        <v>0.5635729105191062</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>0.5712817011187453</v>
+        <v>0.5615182251886836</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>0.5664636974031579</v>
+        <v>0.5598750658046461</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>0.5617350123101492</v>
+        <v>0.5575583711484433</v>
       </c>
       <c r="M22" s="5" t="n">
-        <v>0.557799995169471</v>
+        <v>0.5552890731317713</v>
       </c>
       <c r="N22" s="5" t="n">
-        <v>0.5512309134606482</v>
+        <v>0.5527176570843872</v>
       </c>
     </row>
     <row r="23"/>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -4343,7 +4827,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Табл. 2.9. Коефіцієнти деградації компонентів (за квартал)</t>
+          <t>Table 2.9. Depreciation coefficients d_k (per quarter)</t>
         </is>
       </c>
     </row>
@@ -4351,7 +4835,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Компонент</t>
+          <t>Component</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -4361,14 +4845,14 @@
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Обґрунтування</t>
+          <t>Justification</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C (ядро)</t>
+          <t>C (core)</t>
         </is>
       </c>
       <c r="B4" s="10" t="n">
@@ -4376,7 +4860,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Виробнича компетенція змінюється повільно</t>
+          <t>Production competence changes slowly</t>
         </is>
       </c>
     </row>
@@ -4391,14 +4875,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Плинність кадрів, втрата компетенцій</t>
+          <t>Staff turnover, loss of competencies</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L₂ (матеріали)</t>
+          <t>L₂ (materials)</t>
         </is>
       </c>
       <c r="B6" s="10" t="n">
@@ -4406,14 +4890,14 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Застарівання облікових систем</t>
+          <t>Obsolescence of accounting systems</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L₃ (логістика)</t>
+          <t>L₃ (logistics)</t>
         </is>
       </c>
       <c r="B7" s="10" t="n">
@@ -4421,14 +4905,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Швидка зміна технологій GPS/IoT</t>
+          <t>Fast changes in GPS/IoT technologies</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>L₄ (збут)</t>
+          <t>L₄ (sales)</t>
         </is>
       </c>
       <c r="B8" s="10" t="n">
@@ -4436,14 +4920,14 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Зміна вимог ринку та регуляторів</t>
+          <t>Changes in market and regulatory requirements</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I (інтеграція)</t>
+          <t>I (integration)</t>
         </is>
       </c>
       <c r="B9" s="10" t="n">
@@ -4451,14 +4935,14 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Накопичення несумісностей між системами</t>
+          <t>Accumulating incompatibilities between systems</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S (стратегія)</t>
+          <t>S (strategy)</t>
         </is>
       </c>
       <c r="B10" s="10" t="n">
@@ -4466,7 +4950,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Стратегічна свідомість зберігається довше</t>
+          <t>Strategic awareness persists longer</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4958,7 @@
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
         <is>
-          <t>Джерело: розроблено автором; 2026-04-19 17:32</t>
+          <t>Source: developed by the author; 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -4502,7 +4986,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Траєкторії ADMI за сценаріями (5 років, mean/std/median/p25/p75)</t>
+          <t>ADMI trajectories by scenario (5 years, mean/std/median/p25/p75)</t>
         </is>
       </c>
     </row>
@@ -4510,32 +4994,32 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Бездіяльність</t>
+          <t>Inactivity</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>С-4 Ринкова</t>
+          <t>S-4 Market</t>
         </is>
       </c>
     </row>
@@ -4544,19 +5028,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="5" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
       <c r="C4" s="5" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
       <c r="E4" s="5" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>0.3696603290780116</v>
+        <v>0.3931343578140782</v>
       </c>
     </row>
     <row r="5">
@@ -4564,19 +5048,19 @@
         <v>1</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.3605308704575152</v>
+        <v>0.3837076415283363</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.3758039615378311</v>
+        <v>0.3976494647264437</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.3767424733323877</v>
+        <v>0.3985216267383477</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.3710412993769363</v>
+        <v>0.3935116009518732</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.3739972687997688</v>
+        <v>0.395671893848896</v>
       </c>
     </row>
     <row r="6">
@@ -4584,19 +5068,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.3516656382687368</v>
+        <v>0.3745631699060188</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.3820465038004179</v>
+        <v>0.4023781152920212</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.3837690792431166</v>
+        <v>0.4040848369825167</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.3728300049489147</v>
+        <v>0.3940344953936439</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3782624854318128</v>
+        <v>0.3981351490921974</v>
       </c>
     </row>
     <row r="7">
@@ -4604,19 +5088,19 @@
         <v>3</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.3431129664481376</v>
+        <v>0.3655382118789667</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.3884015171350855</v>
+        <v>0.4070330924140632</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.3904761192158368</v>
+        <v>0.4095844130309628</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.3746367340497398</v>
+        <v>0.3947363994052702</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.3860629747156927</v>
+        <v>0.4037877776660765</v>
       </c>
     </row>
     <row r="8">
@@ -4624,19 +5108,19 @@
         <v>4</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.3345089541626757</v>
+        <v>0.3568102309118118</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.3945549039292197</v>
+        <v>0.4119768772614267</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.3968316438164831</v>
+        <v>0.415138635171817</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.3765285802584857</v>
+        <v>0.3957377174415083</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3933256729694861</v>
+        <v>0.4089497134662814</v>
       </c>
     </row>
     <row r="9">
@@ -4644,19 +5128,19 @@
         <v>5</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.3262024560229315</v>
+        <v>0.3483121580984781</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.4007752089825164</v>
+        <v>0.4169906873110233</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.4028112546500164</v>
+        <v>0.4205541091830805</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.3786041524378011</v>
+        <v>0.3970403666874905</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.39985861456448</v>
+        <v>0.4137630604599687</v>
       </c>
     </row>
     <row r="10"/>
@@ -4670,32 +5154,32 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>Бездіяльність</t>
+          <t>Inactivity</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>С-4 Ринкова</t>
+          <t>S-4 Market</t>
         </is>
       </c>
     </row>
@@ -4704,19 +5188,19 @@
         <v>0</v>
       </c>
       <c r="B13" s="5" t="n">
-        <v>0.1344862205574278</v>
+        <v>0.1221457374077182</v>
       </c>
       <c r="C13" s="5" t="n">
-        <v>0.1344862205574278</v>
+        <v>0.1221457374077182</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>0.1344862205574278</v>
+        <v>0.1221457374077182</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>0.1344862205574278</v>
+        <v>0.1221457374077182</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.1344862205574278</v>
+        <v>0.1221457374077182</v>
       </c>
     </row>
     <row r="14">
@@ -4724,19 +5208,19 @@
         <v>1</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.1314861293420032</v>
+        <v>0.1193942910078471</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.135290140402503</v>
+        <v>0.1230164082026246</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.134830931047028</v>
+        <v>0.1222221163600817</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.1342625653033884</v>
+        <v>0.1220996669703644</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.1348116831575719</v>
+        <v>0.1225642855463422</v>
       </c>
     </row>
     <row r="15">
@@ -4744,19 +5228,19 @@
         <v>2</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.1284862914517003</v>
+        <v>0.1165987795747396</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.1363015306668246</v>
+        <v>0.1240270361414574</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.1352819766556712</v>
+        <v>0.1225590506661903</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.1341038002046211</v>
+        <v>0.1221799312946671</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.1352276713418417</v>
+        <v>0.1232507886891023</v>
       </c>
     </row>
     <row r="16">
@@ -4764,19 +5248,19 @@
         <v>3</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.1254066933931004</v>
+        <v>0.1139812036218986</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.137240688520699</v>
+        <v>0.1250652713120657</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.1355252569023003</v>
+        <v>0.1229083585753478</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.1340289455004239</v>
+        <v>0.1223100416233049</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.1360397192696958</v>
+        <v>0.1238785443962186</v>
       </c>
     </row>
     <row r="17">
@@ -4784,19 +5268,19 @@
         <v>4</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>0.1225294489726381</v>
+        <v>0.1113336311129138</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.1383394635014273</v>
+        <v>0.1260603788133423</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.1359462822609975</v>
+        <v>0.1232540781959381</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.1341546516745399</v>
+        <v>0.1224187158272016</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.1370573841489557</v>
+        <v>0.124528764110823</v>
       </c>
     </row>
     <row r="18">
@@ -4804,26 +5288,26 @@
         <v>5</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>0.1196919018283492</v>
+        <v>0.10884934726155</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.1395928497794712</v>
+        <v>0.1272581153642924</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.1361758709307803</v>
+        <v>0.1236105855767344</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.1343324395117106</v>
+        <v>0.1225694990559587</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.1384419498260514</v>
+        <v>0.1254366319907194</v>
       </c>
     </row>
     <row r="19"/>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -4851,7 +5335,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Покомпонентні DM за сценаріями (середнє, по роках)</t>
+          <t>Per-component DM by scenario (mean, by year)</t>
         </is>
       </c>
     </row>
@@ -4859,14 +5343,14 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Бездіяльність</t>
+          <t>Inactivity</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
@@ -4910,25 +5394,25 @@
         <v>0</v>
       </c>
       <c r="B5" s="5" t="n">
-        <v>0.4324556063611814</v>
+        <v>0.4483838420309389</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.431971899905995</v>
+        <v>0.4319553584170258</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.4159112395184741</v>
+        <v>0.4182939575162374</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.4030528871087627</v>
+        <v>0.4129559751248275</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.3690037249779191</v>
+        <v>0.4090490713476696</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.3598872952072583</v>
+        <v>0.3534445182781272</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.3807721414439693</v>
+        <v>0.4049091174224996</v>
       </c>
     </row>
     <row r="6">
@@ -4936,25 +5420,25 @@
         <v>1</v>
       </c>
       <c r="B6" s="5" t="n">
-        <v>0.4260594071347392</v>
+        <v>0.4419364754249072</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.423403279001444</v>
+        <v>0.4232530112272304</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.4055223599919109</v>
+        <v>0.4075454914867738</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.3912780939917825</v>
+        <v>0.4009717227650416</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.3596998334710151</v>
+        <v>0.3989223288577727</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.3529805680239643</v>
+        <v>0.3463791119672099</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>0.3769264230918647</v>
+        <v>0.4010437790039505</v>
       </c>
     </row>
     <row r="7">
@@ -4962,25 +5446,25 @@
         <v>2</v>
       </c>
       <c r="B7" s="5" t="n">
-        <v>0.4193370286129595</v>
+        <v>0.4352748020157203</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.4152677224540288</v>
+        <v>0.4147025889897403</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.3957285955046173</v>
+        <v>0.3976987080257636</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.3796993025696229</v>
+        <v>0.3888996647142771</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.3508012409883103</v>
+        <v>0.3891575581977389</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.3459262303959569</v>
+        <v>0.3394435611071646</v>
       </c>
       <c r="H7" s="5" t="n">
-        <v>0.3730524864436928</v>
+        <v>0.3968908993503234</v>
       </c>
     </row>
     <row r="8">
@@ -4988,25 +5472,25 @@
         <v>3</v>
       </c>
       <c r="B8" s="5" t="n">
-        <v>0.413251423667457</v>
+        <v>0.4288130749594646</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0.4068941441677206</v>
+        <v>0.406260789055076</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>0.3857118021253765</v>
+        <v>0.3875043524925945</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.3684074258083357</v>
+        <v>0.3772279904443496</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.3425239578139394</v>
+        <v>0.3796322505354439</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.3392663753573569</v>
+        <v>0.3327435373131074</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.3693499818518419</v>
+        <v>0.393006754138133</v>
       </c>
     </row>
     <row r="9">
@@ -5014,25 +5498,25 @@
         <v>4</v>
       </c>
       <c r="B9" s="5" t="n">
-        <v>0.4067394444617909</v>
+        <v>0.4221433817532783</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0.3989739279601052</v>
+        <v>0.3984301963064215</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>0.3760539625642949</v>
+        <v>0.3778112360273818</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.3575133493027609</v>
+        <v>0.3658089105207715</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>0.3338453606745411</v>
+        <v>0.3703526201089538</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.3325738888564541</v>
+        <v>0.3261099835667799</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>0.3654528605062717</v>
+        <v>0.3891918144077552</v>
       </c>
     </row>
     <row r="10">
@@ -5040,39 +5524,39 @@
         <v>5</v>
       </c>
       <c r="B10" s="5" t="n">
-        <v>0.4003850593081164</v>
+        <v>0.4159146594162255</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0.3911126670498661</v>
+        <v>0.3902389878792183</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>0.3665773173810934</v>
+        <v>0.3685102850047615</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.3469901972404624</v>
+        <v>0.3550202851629872</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>0.3254691491272174</v>
+        <v>0.3611761483808724</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.3256617836405353</v>
+        <v>0.3195204382239025</v>
       </c>
       <c r="H10" s="5" t="n">
-        <v>0.361657092410864</v>
+        <v>0.3850094263382479</v>
       </c>
     </row>
     <row r="11"/>
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
@@ -5116,25 +5600,25 @@
         <v>0</v>
       </c>
       <c r="B14" s="5" t="n">
-        <v>0.4324556063611814</v>
+        <v>0.4483838420309389</v>
       </c>
       <c r="C14" s="5" t="n">
-        <v>0.431971899905995</v>
+        <v>0.4319553584170258</v>
       </c>
       <c r="D14" s="5" t="n">
-        <v>0.4159112395184741</v>
+        <v>0.4182939575162374</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>0.4030528871087627</v>
+        <v>0.4129559751248275</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.3690037249779191</v>
+        <v>0.4090490713476696</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.3598872952072583</v>
+        <v>0.3534445182781272</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.3807721414439693</v>
+        <v>0.4049091174224996</v>
       </c>
     </row>
     <row r="15">
@@ -5142,25 +5626,25 @@
         <v>1</v>
       </c>
       <c r="B15" s="5" t="n">
-        <v>0.4433584111565991</v>
+        <v>0.4581512266260088</v>
       </c>
       <c r="C15" s="5" t="n">
-        <v>0.4351274514472215</v>
+        <v>0.4352726763404131</v>
       </c>
       <c r="D15" s="5" t="n">
-        <v>0.4180286606746006</v>
+        <v>0.4200359106715744</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>0.4032035389549001</v>
+        <v>0.4127771156096368</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>0.3715123849254061</v>
+        <v>0.4107610063235118</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.3722913257985445</v>
+        <v>0.3657501129597505</v>
       </c>
       <c r="H15" s="5" t="n">
-        <v>0.391012757165976</v>
+        <v>0.4149082580572028</v>
       </c>
     </row>
     <row r="16">
@@ -5168,25 +5652,25 @@
         <v>2</v>
       </c>
       <c r="B16" s="5" t="n">
-        <v>0.4537370757480793</v>
+        <v>0.4679086349971442</v>
       </c>
       <c r="C16" s="5" t="n">
-        <v>0.4383941487057632</v>
+        <v>0.4388233124002957</v>
       </c>
       <c r="D16" s="5" t="n">
-        <v>0.4199174257137697</v>
+        <v>0.4218830243305469</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>0.40364495775751</v>
+        <v>0.4129028152850139</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.3744548572800155</v>
+        <v>0.4126470734218883</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.384257728801257</v>
+        <v>0.3776467512903754</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>0.4013483963061303</v>
+        <v>0.4247123181944606</v>
       </c>
     </row>
     <row r="17">
@@ -5194,25 +5678,25 @@
         <v>3</v>
       </c>
       <c r="B17" s="5" t="n">
-        <v>0.4640028980144045</v>
+        <v>0.4775748153714439</v>
       </c>
       <c r="C17" s="5" t="n">
-        <v>0.4420843432707101</v>
+        <v>0.4421969599607461</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>0.4221593336925817</v>
+        <v>0.4242967923093445</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>0.4043281039743344</v>
+        <v>0.4131100599148891</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>0.3772708417999583</v>
+        <v>0.4143118842762863</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.3963995734837347</v>
+        <v>0.3896337405176539</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>0.4114872723368864</v>
+        <v>0.4344307739301103</v>
       </c>
     </row>
     <row r="18">
@@ -5220,25 +5704,25 @@
         <v>4</v>
       </c>
       <c r="B18" s="5" t="n">
-        <v>0.474096585962192</v>
+        <v>0.4872681962040858</v>
       </c>
       <c r="C18" s="5" t="n">
-        <v>0.4456156189359028</v>
+        <v>0.446090396371611</v>
       </c>
       <c r="D18" s="5" t="n">
-        <v>0.4243149905390887</v>
+        <v>0.4269725591682956</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.4052776095932338</v>
+        <v>0.4134420511493085</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>0.3800821212154823</v>
+        <v>0.4162115120140469</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.4079954096744913</v>
+        <v>0.4010921326731217</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>0.4212906950248244</v>
+        <v>0.4439924878965663</v>
       </c>
     </row>
     <row r="19">
@@ -5246,39 +5730,39 @@
         <v>5</v>
       </c>
       <c r="B19" s="5" t="n">
-        <v>0.4842136850074039</v>
+        <v>0.4968859800188802</v>
       </c>
       <c r="C19" s="5" t="n">
-        <v>0.4493725372515353</v>
+        <v>0.4502101137430297</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>0.4267112843642416</v>
+        <v>0.4295727316853429</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.4062636269387966</v>
+        <v>0.4140977691180214</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.3826469694046506</v>
+        <v>0.4181873262399166</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.4193691077550387</v>
+        <v>0.4126425952732784</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>0.4312003057485995</v>
+        <v>0.4532678327211507</v>
       </c>
     </row>
     <row r="20"/>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
@@ -5322,25 +5806,25 @@
         <v>0</v>
       </c>
       <c r="B23" s="5" t="n">
-        <v>0.4324556063611814</v>
+        <v>0.4483838420309389</v>
       </c>
       <c r="C23" s="5" t="n">
-        <v>0.431971899905995</v>
+        <v>0.4319553584170258</v>
       </c>
       <c r="D23" s="5" t="n">
-        <v>0.4159112395184741</v>
+        <v>0.4182939575162374</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>0.4030528871087627</v>
+        <v>0.4129559751248275</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>0.3690037249779191</v>
+        <v>0.4090490713476696</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.3598872952072583</v>
+        <v>0.3534445182781272</v>
       </c>
       <c r="H23" s="5" t="n">
-        <v>0.3807721414439693</v>
+        <v>0.4049091174224996</v>
       </c>
     </row>
     <row r="24">
@@ -5348,25 +5832,25 @@
         <v>1</v>
       </c>
       <c r="B24" s="5" t="n">
-        <v>0.4621182387101967</v>
+        <v>0.4767681218198833</v>
       </c>
       <c r="C24" s="5" t="n">
-        <v>0.4411000484854359</v>
+        <v>0.4412883837456772</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>0.4141352858962374</v>
+        <v>0.4164661689990189</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.3954118926919097</v>
+        <v>0.4045349814739223</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>0.3638157019806292</v>
+        <v>0.4030984918774884</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.3723233345728374</v>
+        <v>0.3654760501839208</v>
       </c>
       <c r="H24" s="5" t="n">
-        <v>0.3843050646583548</v>
+        <v>0.4081606619296902</v>
       </c>
     </row>
     <row r="25">
@@ -5374,25 +5858,25 @@
         <v>2</v>
       </c>
       <c r="B25" s="5" t="n">
-        <v>0.4907709513863031</v>
+        <v>0.5043995323723667</v>
       </c>
       <c r="C25" s="5" t="n">
-        <v>0.4510153216377</v>
+        <v>0.4513452681436545</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>0.4125467743037092</v>
+        <v>0.4152725923410324</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.3882369436689242</v>
+        <v>0.3970703282445395</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>0.3590176915944754</v>
+        <v>0.3972931483963012</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.3845044720564693</v>
+        <v>0.3774539555422756</v>
       </c>
       <c r="H25" s="5" t="n">
-        <v>0.3881941614239974</v>
+        <v>0.4113965466197599</v>
       </c>
     </row>
     <row r="26">
@@ -5400,25 +5884,25 @@
         <v>3</v>
       </c>
       <c r="B26" s="5" t="n">
-        <v>0.5185673202377186</v>
+        <v>0.531532164345216</v>
       </c>
       <c r="C26" s="5" t="n">
-        <v>0.4613013787453195</v>
+        <v>0.4618067118019675</v>
       </c>
       <c r="D26" s="5" t="n">
-        <v>0.4114762033138881</v>
+        <v>0.4141825010516722</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>0.3812114305716073</v>
+        <v>0.3899362672588457</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>0.3544489525027588</v>
+        <v>0.3915898369692657</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.3962649096966742</v>
+        <v>0.3891036709864813</v>
       </c>
       <c r="H26" s="5" t="n">
-        <v>0.3917594924068205</v>
+        <v>0.4149207328540409</v>
       </c>
     </row>
     <row r="27">
@@ -5426,25 +5910,25 @@
         <v>4</v>
       </c>
       <c r="B27" s="5" t="n">
-        <v>0.5456946711258496</v>
+        <v>0.5574137891636539</v>
       </c>
       <c r="C27" s="5" t="n">
-        <v>0.4719666967934915</v>
+        <v>0.4728889922573165</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>0.4107517750291753</v>
+        <v>0.4137111100619261</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.3745837552525066</v>
+        <v>0.3829956862652699</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>0.3500904454411213</v>
+        <v>0.3861806657601805</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.4077123016126389</v>
+        <v>0.400309783020707</v>
       </c>
       <c r="H27" s="5" t="n">
-        <v>0.3954261976067559</v>
+        <v>0.4181666538655811</v>
       </c>
     </row>
     <row r="28">
@@ -5452,39 +5936,39 @@
         <v>5</v>
       </c>
       <c r="B28" s="5" t="n">
-        <v>0.57170371246795</v>
+        <v>0.582512231692296</v>
       </c>
       <c r="C28" s="5" t="n">
-        <v>0.4829393532137277</v>
+        <v>0.4841467443659926</v>
       </c>
       <c r="D28" s="5" t="n">
-        <v>0.4103036258504539</v>
+        <v>0.413252858631375</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>0.3683930647241552</v>
+        <v>0.376296472675313</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>0.3459456188065548</v>
+        <v>0.381012794970687</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.4187899659179348</v>
+        <v>0.4112862086872531</v>
       </c>
       <c r="H28" s="5" t="n">
-        <v>0.3990470136124556</v>
+        <v>0.4215687288327747</v>
       </c>
     </row>
     <row r="29"/>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
@@ -5528,25 +6012,25 @@
         <v>0</v>
       </c>
       <c r="B32" s="5" t="n">
-        <v>0.4324556063611814</v>
+        <v>0.4483838420309389</v>
       </c>
       <c r="C32" s="5" t="n">
-        <v>0.431971899905995</v>
+        <v>0.4319553584170258</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>0.4159112395184741</v>
+        <v>0.4182939575162374</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0.4030528871087627</v>
+        <v>0.4129559751248275</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.3690037249779191</v>
+        <v>0.4090490713476696</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.3598872952072583</v>
+        <v>0.3534445182781272</v>
       </c>
       <c r="H32" s="5" t="n">
-        <v>0.3807721414439693</v>
+        <v>0.4049091174224996</v>
       </c>
     </row>
     <row r="33">
@@ -5554,25 +6038,25 @@
         <v>1</v>
       </c>
       <c r="B33" s="5" t="n">
-        <v>0.4381434780904441</v>
+        <v>0.453591554458617</v>
       </c>
       <c r="C33" s="5" t="n">
-        <v>0.4315327741920389</v>
+        <v>0.4320273895347493</v>
       </c>
       <c r="D33" s="5" t="n">
-        <v>0.414107161151917</v>
+        <v>0.4165343519038279</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>0.3992180229327482</v>
+        <v>0.4091425581894577</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.3681113000845623</v>
+        <v>0.4069095432083563</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.4007335854505067</v>
+        <v>0.3936019545267553</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>0.3912012468563042</v>
+        <v>0.4148719067648846</v>
       </c>
     </row>
     <row r="34">
@@ -5580,25 +6064,25 @@
         <v>2</v>
       </c>
       <c r="B34" s="5" t="n">
-        <v>0.4442366078847409</v>
+        <v>0.4588413298504811</v>
       </c>
       <c r="C34" s="5" t="n">
-        <v>0.4315507254667366</v>
+        <v>0.4322065651957306</v>
       </c>
       <c r="D34" s="5" t="n">
-        <v>0.4125743690187642</v>
+        <v>0.414734305688116</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>0.3958814194682423</v>
+        <v>0.40565643201159</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.3674619290701409</v>
+        <v>0.4050284053133669</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.439368475901781</v>
+        <v>0.4319825075128227</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>0.4013814736427619</v>
+        <v>0.4247309662855531</v>
       </c>
     </row>
     <row r="35">
@@ -5606,25 +6090,25 @@
         <v>3</v>
       </c>
       <c r="B35" s="5" t="n">
-        <v>0.450112618189053</v>
+        <v>0.4642968881301808</v>
       </c>
       <c r="C35" s="5" t="n">
-        <v>0.4315566696609205</v>
+        <v>0.4325431638699458</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>0.4111825822811908</v>
+        <v>0.4133539365975332</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>0.3928669267593836</v>
+        <v>0.4021147708829864</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>0.3669576967747111</v>
+        <v>0.4033199615610862</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.4764566980729816</v>
+        <v>0.4685771423330817</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>0.4114203315432326</v>
+        <v>0.4346770323065947</v>
       </c>
     </row>
     <row r="36">
@@ -5632,25 +6116,25 @@
         <v>4</v>
       </c>
       <c r="B36" s="5" t="n">
-        <v>0.4563181713478389</v>
+        <v>0.4699007084555509</v>
       </c>
       <c r="C36" s="5" t="n">
-        <v>0.4319655460147288</v>
+        <v>0.4331690730901638</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>0.41012495253985</v>
+        <v>0.4124244461327198</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>0.3899259640622988</v>
+        <v>0.399203787189037</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.3662524917208997</v>
+        <v>0.4017755880949417</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.5119208052928801</v>
+        <v>0.5037367622346989</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>0.4213064741629619</v>
+        <v>0.4439740959513193</v>
       </c>
     </row>
     <row r="37">
@@ -5658,39 +6142,39 @@
         <v>5</v>
       </c>
       <c r="B37" s="5" t="n">
-        <v>0.4624327223517494</v>
+        <v>0.4755940260484063</v>
       </c>
       <c r="C37" s="5" t="n">
-        <v>0.4324864432645233</v>
+        <v>0.4340990411539536</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>0.4092496292418277</v>
+        <v>0.4115355470476794</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>0.3875163407387333</v>
+        <v>0.3965975742389583</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.3657360886346943</v>
+        <v>0.4008569952025799</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.5454526062282885</v>
+        <v>0.5370930006514132</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.4308980345119556</v>
+        <v>0.4532542955596361</v>
       </c>
     </row>
     <row r="38"/>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>С-4 Ринкова</t>
+          <t>S-4 Market</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
@@ -5734,25 +6218,25 @@
         <v>0</v>
       </c>
       <c r="B41" s="5" t="n">
-        <v>0.4324556063611814</v>
+        <v>0.4483838420309389</v>
       </c>
       <c r="C41" s="5" t="n">
-        <v>0.431971899905995</v>
+        <v>0.4319553584170258</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>0.4159112395184741</v>
+        <v>0.4182939575162374</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>0.4030528871087627</v>
+        <v>0.4129559751248275</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>0.3690037249779191</v>
+        <v>0.4090490713476696</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.3598872952072583</v>
+        <v>0.3534445182781272</v>
       </c>
       <c r="H41" s="5" t="n">
-        <v>0.3807721414439693</v>
+        <v>0.4049091174224996</v>
       </c>
     </row>
     <row r="42">
@@ -5760,25 +6244,25 @@
         <v>1</v>
       </c>
       <c r="B42" s="5" t="n">
-        <v>0.432423002465583</v>
+        <v>0.4481912219721899</v>
       </c>
       <c r="C42" s="5" t="n">
-        <v>0.4275075347105776</v>
+        <v>0.4281686470091213</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>0.4140216521011799</v>
+        <v>0.4163247773651873</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>0.4033478222271015</v>
+        <v>0.4127421181825999</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.3815030255343514</v>
+        <v>0.4200978309306105</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.3780049973075137</v>
+        <v>0.3712041093715788</v>
       </c>
       <c r="H42" s="5" t="n">
-        <v>0.3975598189673263</v>
+        <v>0.4209668827547176</v>
       </c>
     </row>
     <row r="43">
@@ -5786,25 +6270,25 @@
         <v>2</v>
       </c>
       <c r="B43" s="5" t="n">
-        <v>0.4327423870967532</v>
+        <v>0.4480467055731154</v>
       </c>
       <c r="C43" s="5" t="n">
-        <v>0.4235417400943995</v>
+        <v>0.4242681495062886</v>
       </c>
       <c r="D43" s="5" t="n">
-        <v>0.4121195109949514</v>
+        <v>0.4143716304243525</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>0.403555145109111</v>
+        <v>0.4127086422912259</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>0.3937825200745187</v>
+        <v>0.430802230301351</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.3959313124485039</v>
+        <v>0.388685262269836</v>
       </c>
       <c r="H43" s="5" t="n">
-        <v>0.4138792429678229</v>
+        <v>0.436627739526836</v>
       </c>
     </row>
     <row r="44">
@@ -5812,25 +6296,25 @@
         <v>3</v>
       </c>
       <c r="B44" s="5" t="n">
-        <v>0.433070002827726</v>
+        <v>0.4481862759493301</v>
       </c>
       <c r="C44" s="5" t="n">
-        <v>0.4197066589009457</v>
+        <v>0.4203230958197141</v>
       </c>
       <c r="D44" s="5" t="n">
-        <v>0.4106364384452381</v>
+        <v>0.4124137440242104</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>0.4037543922025758</v>
+        <v>0.4130295233857585</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.4190706824710083</v>
+        <v>0.4547857199832908</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.4132080557627231</v>
+        <v>0.4060795814587591</v>
       </c>
       <c r="H44" s="5" t="n">
-        <v>0.4298160455180654</v>
+        <v>0.4522971503458577</v>
       </c>
     </row>
     <row r="45">
@@ -5838,25 +6322,25 @@
         <v>4</v>
       </c>
       <c r="B45" s="5" t="n">
-        <v>0.4332377754625379</v>
+        <v>0.4480000579270083</v>
       </c>
       <c r="C45" s="5" t="n">
-        <v>0.4157853375548787</v>
+        <v>0.4165547031547449</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>0.409061217228453</v>
+        <v>0.4110987935369448</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>0.4041357504729084</v>
+        <v>0.4130609209306236</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>0.4435081896662315</v>
+        <v>0.4776771272325931</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.4303162909447939</v>
+        <v>0.4231534186472086</v>
       </c>
       <c r="H45" s="5" t="n">
-        <v>0.4454914967823498</v>
+        <v>0.4675383306240913</v>
       </c>
     </row>
     <row r="46">
@@ -5864,32 +6348,32 @@
         <v>5</v>
       </c>
       <c r="B46" s="5" t="n">
-        <v>0.4333798667041744</v>
+        <v>0.4480958198502777</v>
       </c>
       <c r="C46" s="5" t="n">
-        <v>0.4117255582189136</v>
+        <v>0.4126432449161025</v>
       </c>
       <c r="D46" s="5" t="n">
-        <v>0.4075658829903521</v>
+        <v>0.4095638780235318</v>
       </c>
       <c r="E46" s="5" t="n">
-        <v>0.4043798335838054</v>
+        <v>0.4129529170725926</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.4666998622414589</v>
+        <v>0.4998499580705074</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.4471232159913421</v>
+        <v>0.4397309591835246</v>
       </c>
       <c r="H46" s="5" t="n">
-        <v>0.4606806143340989</v>
+        <v>0.4825207110735795</v>
       </c>
     </row>
     <row r="47"/>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -5917,7 +6401,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Розподіл підприємств по рівнях (за сценаріями та роками)</t>
+          <t>Enterprise distribution by level (by scenario and year)</t>
         </is>
       </c>
     </row>
@@ -5925,39 +6409,39 @@
     <row r="3">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>Бездіяльність</t>
+          <t>Inactivity</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
@@ -5966,16 +6450,16 @@
         <v>0</v>
       </c>
       <c r="B5" s="12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>0.345</v>
+        <v>0.405</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F5" s="12" t="n">
         <v>0</v>
@@ -5986,13 +6470,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="12" t="n">
-        <v>0.095</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.51</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>0.285</v>
+        <v>0.36</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0.06</v>
@@ -6006,16 +6490,16 @@
         <v>2</v>
       </c>
       <c r="B7" s="12" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>0.585</v>
+        <v>0.58</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>0.25</v>
+        <v>0.295</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>0.055</v>
+        <v>0.045</v>
       </c>
       <c r="F7" s="12" t="n">
         <v>0</v>
@@ -6026,13 +6510,13 @@
         <v>3</v>
       </c>
       <c r="B8" s="12" t="n">
-        <v>0.11</v>
+        <v>0.08</v>
       </c>
       <c r="C8" s="12" t="n">
         <v>0.605</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>0.045</v>
@@ -6046,16 +6530,16 @@
         <v>4</v>
       </c>
       <c r="B9" s="12" t="n">
-        <v>0.13</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>0.625</v>
+        <v>0.65</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>0.21</v>
+        <v>0.225</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="F9" s="12" t="n">
         <v>0</v>
@@ -6066,16 +6550,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="12" t="n">
-        <v>0.15</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>0.635</v>
+        <v>0.67</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>0.185</v>
+        <v>0.205</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="F10" s="12" t="n">
         <v>0</v>
@@ -6085,39 +6569,39 @@
     <row r="12">
       <c r="A12" s="11" t="inlineStr">
         <is>
-          <t>Рівномірна</t>
+          <t>Uniform</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
@@ -6126,16 +6610,16 @@
         <v>0</v>
       </c>
       <c r="B14" s="12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C14" s="12" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
       <c r="D14" s="12" t="n">
-        <v>0.345</v>
+        <v>0.405</v>
       </c>
       <c r="E14" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F14" s="12" t="n">
         <v>0</v>
@@ -6146,16 +6630,16 @@
         <v>1</v>
       </c>
       <c r="B15" s="12" t="n">
-        <v>0.09</v>
+        <v>0.065</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>0.465</v>
+        <v>0.445</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F15" s="12" t="n">
         <v>0</v>
@@ -6166,13 +6650,13 @@
         <v>2</v>
       </c>
       <c r="B16" s="12" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>0.44</v>
+        <v>0.415</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>0.415</v>
+        <v>0.455</v>
       </c>
       <c r="E16" s="12" t="n">
         <v>0.065</v>
@@ -6186,13 +6670,13 @@
         <v>3</v>
       </c>
       <c r="B17" s="12" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>0.435</v>
+        <v>0.405</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="E17" s="12" t="n">
         <v>0.07000000000000001</v>
@@ -6206,13 +6690,13 @@
         <v>4</v>
       </c>
       <c r="B18" s="12" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>0.425</v>
+        <v>0.365</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>0.07000000000000001</v>
@@ -6226,13 +6710,13 @@
         <v>5</v>
       </c>
       <c r="B19" s="12" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>0.385</v>
+        <v>0.36</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>0.47</v>
+        <v>0.505</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>0.07000000000000001</v>
@@ -6245,39 +6729,39 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>С-2 Ядро</t>
+          <t>S-2 Core</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
@@ -6286,16 +6770,16 @@
         <v>0</v>
       </c>
       <c r="B23" s="12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.345</v>
+        <v>0.405</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -6306,16 +6790,16 @@
         <v>1</v>
       </c>
       <c r="B24" s="12" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="C24" s="12" t="n">
-        <v>0.47</v>
+        <v>0.445</v>
       </c>
       <c r="D24" s="12" t="n">
-        <v>0.38</v>
+        <v>0.435</v>
       </c>
       <c r="E24" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F24" s="12" t="n">
         <v>0</v>
@@ -6326,16 +6810,16 @@
         <v>2</v>
       </c>
       <c r="B25" s="12" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
       <c r="C25" s="12" t="n">
-        <v>0.46</v>
+        <v>0.41</v>
       </c>
       <c r="D25" s="12" t="n">
-        <v>0.395</v>
+        <v>0.455</v>
       </c>
       <c r="E25" s="12" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F25" s="12" t="n">
         <v>0</v>
@@ -6346,13 +6830,13 @@
         <v>3</v>
       </c>
       <c r="B26" s="12" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="C26" s="12" t="n">
-        <v>0.435</v>
+        <v>0.385</v>
       </c>
       <c r="D26" s="12" t="n">
-        <v>0.42</v>
+        <v>0.485</v>
       </c>
       <c r="E26" s="12" t="n">
         <v>0.07000000000000001</v>
@@ -6366,13 +6850,13 @@
         <v>4</v>
       </c>
       <c r="B27" s="12" t="n">
-        <v>0.075</v>
+        <v>0.055</v>
       </c>
       <c r="C27" s="12" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="D27" s="12" t="n">
-        <v>0.455</v>
+        <v>0.525</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>0.07000000000000001</v>
@@ -6386,13 +6870,13 @@
         <v>5</v>
       </c>
       <c r="B28" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>0.37</v>
+        <v>0.34</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>0.49</v>
+        <v>0.535</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>0.07000000000000001</v>
@@ -6405,39 +6889,39 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>С-3 Інтеграція</t>
+          <t>S-3 Integration</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
@@ -6446,16 +6930,16 @@
         <v>0</v>
       </c>
       <c r="B32" s="12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C32" s="12" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
       <c r="D32" s="12" t="n">
-        <v>0.345</v>
+        <v>0.405</v>
       </c>
       <c r="E32" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F32" s="12" t="n">
         <v>0</v>
@@ -6466,16 +6950,16 @@
         <v>1</v>
       </c>
       <c r="B33" s="12" t="n">
-        <v>0.09</v>
+        <v>0.065</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>0.49</v>
+        <v>0.475</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>0.355</v>
+        <v>0.4</v>
       </c>
       <c r="E33" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>0</v>
@@ -6486,16 +6970,16 @@
         <v>2</v>
       </c>
       <c r="B34" s="12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>0.48</v>
+        <v>0.465</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>0.365</v>
+        <v>0.405</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F34" s="12" t="n">
         <v>0</v>
@@ -6506,16 +6990,16 @@
         <v>3</v>
       </c>
       <c r="B35" s="12" t="n">
-        <v>0.09</v>
+        <v>0.065</v>
       </c>
       <c r="C35" s="12" t="n">
-        <v>0.46</v>
+        <v>0.455</v>
       </c>
       <c r="D35" s="12" t="n">
-        <v>0.385</v>
+        <v>0.42</v>
       </c>
       <c r="E35" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F35" s="12" t="n">
         <v>0</v>
@@ -6526,16 +7010,16 @@
         <v>4</v>
       </c>
       <c r="B36" s="12" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="C36" s="12" t="n">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="D36" s="12" t="n">
-        <v>0.41</v>
+        <v>0.425</v>
       </c>
       <c r="E36" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F36" s="12" t="n">
         <v>0</v>
@@ -6546,16 +7030,16 @@
         <v>5</v>
       </c>
       <c r="B37" s="12" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="C37" s="12" t="n">
         <v>0.44</v>
       </c>
       <c r="D37" s="12" t="n">
-        <v>0.41</v>
+        <v>0.435</v>
       </c>
       <c r="E37" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F37" s="12" t="n">
         <v>0</v>
@@ -6565,39 +7049,39 @@
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>С-4 Ринкова</t>
+          <t>S-4 Market</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Рік</t>
+          <t>Year</t>
         </is>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>Рівень 1</t>
+          <t>Level 1</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Рівень 2</t>
+          <t>Level 2</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Рівень 3</t>
+          <t>Level 3</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Рівень 4</t>
+          <t>Level 4</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Рівень 5</t>
+          <t>Level 5</t>
         </is>
       </c>
     </row>
@@ -6606,16 +7090,16 @@
         <v>0</v>
       </c>
       <c r="B41" s="12" t="n">
-        <v>0.09</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C41" s="12" t="n">
-        <v>0.5</v>
+        <v>0.465</v>
       </c>
       <c r="D41" s="12" t="n">
-        <v>0.345</v>
+        <v>0.405</v>
       </c>
       <c r="E41" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F41" s="12" t="n">
         <v>0</v>
@@ -6626,16 +7110,16 @@
         <v>1</v>
       </c>
       <c r="B42" s="12" t="n">
-        <v>0.09</v>
+        <v>0.065</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>0.46</v>
+        <v>0.45</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>0.385</v>
+        <v>0.425</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F42" s="12" t="n">
         <v>0</v>
@@ -6646,16 +7130,16 @@
         <v>2</v>
       </c>
       <c r="B43" s="12" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.065</v>
       </c>
       <c r="C43" s="12" t="n">
-        <v>0.445</v>
+        <v>0.44</v>
       </c>
       <c r="D43" s="12" t="n">
-        <v>0.405</v>
+        <v>0.435</v>
       </c>
       <c r="E43" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F43" s="12" t="n">
         <v>0</v>
@@ -6666,16 +7150,16 @@
         <v>3</v>
       </c>
       <c r="B44" s="12" t="n">
-        <v>0.08</v>
+        <v>0.065</v>
       </c>
       <c r="C44" s="12" t="n">
         <v>0.405</v>
       </c>
       <c r="D44" s="12" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="E44" s="12" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="F44" s="12" t="n">
         <v>0</v>
@@ -6686,16 +7170,16 @@
         <v>4</v>
       </c>
       <c r="B45" s="12" t="n">
-        <v>0.075</v>
+        <v>0.065</v>
       </c>
       <c r="C45" s="12" t="n">
         <v>0.39</v>
       </c>
       <c r="D45" s="12" t="n">
-        <v>0.47</v>
+        <v>0.475</v>
       </c>
       <c r="E45" s="12" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F45" s="12" t="n">
         <v>0</v>
@@ -6706,16 +7190,16 @@
         <v>5</v>
       </c>
       <c r="B46" s="12" t="n">
-        <v>0.075</v>
+        <v>0.06</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>0.37</v>
+        <v>0.375</v>
       </c>
       <c r="D46" s="12" t="n">
-        <v>0.49</v>
+        <v>0.495</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>0.065</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F46" s="12" t="n">
         <v>0</v>
@@ -6725,7 +7209,7 @@
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -6753,7 +7237,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Матриця переходу Маркова — Рівномірна (річна)</t>
+          <t>Markov transition matrix — Uniform (annual)</t>
         </is>
       </c>
     </row>
@@ -6761,7 +7245,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>З рівня / На рівень</t>
+          <t>From / To level</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -6793,14 +7277,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1 (аналоговий)</t>
+          <t>1 (analog)</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>0.95</v>
+        <v>0.9361702127659575</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>0.05</v>
+        <v>0.06382978723404255</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>0</v>
@@ -6815,17 +7299,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2 (фрагментарний)</t>
+          <t>2 (fragmented)</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>0.00498663673913295</v>
+        <v>0.004988360492184902</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.9093959343291181</v>
+        <v>0.9418024609245095</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.08561742893174902</v>
+        <v>0.05320917858330563</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>0</v>
@@ -6837,20 +7321,20 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3 (інтегрований)</t>
+          <t>3 (integrated)</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.007462500932812617</v>
+        <v>0.004996741255702803</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.9875376234422029</v>
+        <v>0.9863132739517706</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.004999875624984453</v>
+        <v>0.008689984792526613</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>0</v>
@@ -6859,7 +7343,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4 (адаптивний)</t>
+          <t>4 (adaptive)</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -6881,7 +7365,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5 (інтелектуальний)</t>
+          <t>5 (intelligent)</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -6904,7 +7388,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
@@ -6944,7 +7428,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Матриця переходу Маркова — С-2 Ядро (річна)</t>
+          <t>Markov transition matrix — S-2 Core (annual)</t>
         </is>
       </c>
     </row>
@@ -6952,7 +7436,7 @@
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>З рівня / На рівень</t>
+          <t>From / To level</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -6984,14 +7468,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>1 (аналоговий)</t>
+          <t>1 (analog)</t>
         </is>
       </c>
       <c r="B4" s="13" t="n">
-        <v>0.9285714285714286</v>
+        <v>0.8902439024390244</v>
       </c>
       <c r="C4" s="13" t="n">
-        <v>0.07142857142857142</v>
+        <v>0.1097560975609756</v>
       </c>
       <c r="D4" s="13" t="n">
         <v>0</v>
@@ -7006,17 +7490,17 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>2 (фрагментарний)</t>
+          <t>2 (fragmented)</t>
         </is>
       </c>
       <c r="B5" s="13" t="n">
-        <v>0.004986690534587173</v>
+        <v>0.004975124378109453</v>
       </c>
       <c r="C5" s="13" t="n">
-        <v>0.9020214113845331</v>
+        <v>0.9300754712079289</v>
       </c>
       <c r="D5" s="13" t="n">
-        <v>0.09299189808087971</v>
+        <v>0.06494940441396152</v>
       </c>
       <c r="E5" s="13" t="n">
         <v>0</v>
@@ -7028,20 +7512,20 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>3 (інтегрований)</t>
+          <t>3 (integrated)</t>
         </is>
       </c>
       <c r="B6" s="13" t="n">
         <v>0</v>
       </c>
       <c r="C6" s="13" t="n">
-        <v>0.007389162561576354</v>
+        <v>0.004975124378109453</v>
       </c>
       <c r="D6" s="13" t="n">
-        <v>0.9852216748768473</v>
+        <v>0.9864470749699776</v>
       </c>
       <c r="E6" s="13" t="n">
-        <v>0.007389162561576354</v>
+        <v>0.008577800651912848</v>
       </c>
       <c r="F6" s="13" t="n">
         <v>0</v>
@@ -7050,7 +7534,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>4 (адаптивний)</t>
+          <t>4 (adaptive)</t>
         </is>
       </c>
       <c r="B7" s="13" t="n">
@@ -7072,7 +7556,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>5 (інтелектуальний)</t>
+          <t>5 (intelligent)</t>
         </is>
       </c>
       <c r="B8" s="13" t="n">
@@ -7095,7 +7579,7 @@
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Джерело: імітаційне моделювання, 2026-04-19 17:32</t>
+          <t>Source: simulation results, 2026-10-10 10:34</t>
         </is>
       </c>
     </row>
